--- a/plots/countries/sectors/Bhutan-sectors.xlsx
+++ b/plots/countries/sectors/Bhutan-sectors.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">Author</t>
   </si>
@@ -30,13 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2025). Tidy GHG Inventories (1.0) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14945466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See also</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
@@ -443,14 +437,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -464,39 +450,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
       </c>
       <c r="D2" t="n">
         <v>2019</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
         <v>0.0776558827379189</v>
@@ -504,19 +490,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>2019</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0.046322863884</v>
@@ -524,19 +510,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
         <v>2019</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>0.00029491763616</v>
@@ -544,19 +530,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
         <v>2019</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>0.0966167698356</v>
@@ -564,19 +550,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>2019</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -584,19 +570,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
         <v>2019</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
         <v>0.504694304409</v>
@@ -604,19 +590,19 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>2019</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
         <v>0.61284171345</v>
@@ -624,19 +610,19 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
         <v>2019</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
         <v>-12.0106577878486</v>
@@ -644,19 +630,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>2019</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
         <v>0.0935817209218702</v>
@@ -664,19 +650,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
       </c>
       <c r="D11" t="n">
         <v>2020</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>0.0761118657697275</v>
@@ -684,19 +670,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>2020</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
         <v>0.0396982843075</v>
@@ -704,19 +690,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
         <v>2020</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
         <v>0.000171989188032</v>
@@ -724,19 +710,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
         <v>2020</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
         <v>0.1893655440396</v>
@@ -744,19 +730,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
         <v>2020</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -764,19 +750,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
         <v>2020</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
         <v>0.3770919422034</v>
@@ -784,19 +770,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
         <v>2020</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
         <v>0.69382107345</v>
@@ -804,19 +790,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
         <v>2020</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
         <v>-11.4229039290333</v>
@@ -824,19 +810,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
         <v>2020</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
         <v>0.0950080320238746</v>
@@ -844,19 +830,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
         <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>2021</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
         <v>0.0711456563442429</v>
@@ -864,19 +850,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
         <v>2021</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
         <v>0.009730802699</v>
@@ -884,19 +870,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
         <v>2021</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>0.00024629067552</v>
@@ -904,19 +890,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D23" t="n">
         <v>2021</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
         <v>0.216110200453656</v>
@@ -924,19 +910,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
         <v>2021</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -944,19 +930,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
         <v>2021</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
         <v>0.3855738378516</v>
@@ -964,19 +950,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
         <v>2021</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
         <v>0.698346169734667</v>
@@ -984,19 +970,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
         <v>2021</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
         <v>-11.7111026958737</v>
@@ -1004,19 +990,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D28" t="n">
         <v>2021</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
         <v>0.0967401135369864</v>
@@ -1024,19 +1010,19 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
         <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" t="s">
-        <v>16</v>
       </c>
       <c r="D29" t="n">
         <v>2022</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F29" t="n">
         <v>0.0657858558680788</v>
@@ -1044,19 +1030,19 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
         <v>2022</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
         <v>0.027840783315</v>
@@ -1064,19 +1050,19 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31" t="n">
         <v>2022</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
         <v>0.00035019599808</v>
@@ -1084,19 +1070,19 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D32" t="n">
         <v>2022</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F32" t="n">
         <v>0.1525937993784</v>
@@ -1104,19 +1090,19 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D33" t="n">
         <v>2022</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1124,19 +1110,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D34" t="n">
         <v>2022</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F34" t="n">
         <v>0.3785969210748</v>
@@ -1144,19 +1130,19 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D35" t="n">
         <v>2022</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F35" t="n">
         <v>0.673933361316667</v>
@@ -1164,19 +1150,19 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D36" t="n">
         <v>2022</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
         <v>-11.3305169372687</v>
@@ -1184,19 +1170,19 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D37" t="n">
         <v>2022</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
         <v>0.099010591092565</v>

--- a/plots/countries/sectors/Bhutan-sectors.xlsx
+++ b/plots/countries/sectors/Bhutan-sectors.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2.1) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
